--- a/العيال اللي مجبوش الرقم القومي/New Microsoft Excel Worksheet.xlsx
+++ b/العيال اللي مجبوش الرقم القومي/New Microsoft Excel Worksheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28014"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E9EBD4-F7E7-4B1A-8DD8-983779A6AFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD238BD-CE81-4165-9486-080A75C9D212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="207">
   <si>
     <t xml:space="preserve">مريم سعيد تواضروس ابراهيم </t>
   </si>
@@ -634,17 +633,36 @@
   </si>
   <si>
     <t>ابونا بيشوي يشوع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المرحلة الثانية </t>
+  </si>
+  <si>
+    <t>اسرة الانبا انطونيوس</t>
+  </si>
+  <si>
+    <t>ابونا  سوريال</t>
+  </si>
+  <si>
+    <t>شارع ابو صابر 35</t>
+  </si>
+  <si>
+    <t>01282994801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شنودة عادل أبرهيم ادم </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="00000000000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -758,6 +776,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -873,7 +898,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1019,6 +1044,27 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1026,21 +1072,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -1051,14 +1083,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="3" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1338,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
@@ -3644,7 +3669,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="23" t="s">
         <v>162</v>
       </c>
@@ -3679,7 +3704,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C66" s="23" t="s">
         <v>163</v>
       </c>
@@ -3714,7 +3739,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C67" s="23" t="s">
         <v>165</v>
       </c>
@@ -3749,7 +3774,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C68" s="23" t="s">
         <v>167</v>
       </c>
@@ -3784,7 +3809,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C69" s="23" t="s">
         <v>169</v>
       </c>
@@ -3819,7 +3844,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C70" s="23" t="s">
         <v>171</v>
       </c>
@@ -3854,7 +3879,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C71" s="23" t="s">
         <v>173</v>
       </c>
@@ -3881,7 +3906,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="72" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A72" s="37"/>
       <c r="B72" s="37"/>
       <c r="C72" s="38" t="s">
@@ -3920,7 +3945,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="73" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A73" s="37"/>
       <c r="B73" s="37"/>
       <c r="C73" s="38" t="s">
@@ -3959,7 +3984,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A74" s="37"/>
       <c r="B74" s="37"/>
       <c r="C74" s="38" t="s">
@@ -3996,7 +4021,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A75" s="37"/>
       <c r="B75" s="37"/>
       <c r="C75" s="38" t="s">
@@ -4033,7 +4058,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="76" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A76" s="37"/>
       <c r="B76" s="37"/>
       <c r="C76" s="38" t="s">
@@ -4070,7 +4095,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A77" s="37"/>
       <c r="B77" s="37"/>
       <c r="C77" s="38" t="s">
@@ -4107,7 +4132,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:15" s="43" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" s="43" customFormat="1" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="37"/>
       <c r="B78" s="37"/>
       <c r="C78" s="47" t="s">
@@ -4146,24 +4171,64 @@
         <v>180</v>
       </c>
     </row>
+    <row r="79" spans="1:19" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="57">
+        <v>46161.515455312503</v>
+      </c>
+      <c r="B79" s="57"/>
+      <c r="C79" s="57" t="str">
+        <f>RIGHT(I79,7)</f>
+        <v/>
+      </c>
+      <c r="D79" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="E79" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="F79" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="G79" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="H79" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="I79" s="55"/>
+      <c r="J79" s="54">
+        <v>46161</v>
+      </c>
+      <c r="K79" s="26">
+        <v>44835</v>
+      </c>
+      <c r="L79" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O79" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="P79" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q79" s="51"/>
+      <c r="R79" s="51"/>
+      <c r="S79" s="51"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H12:I13">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="C72:C78">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:I71">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:I14">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:I71">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C72:C78">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
